--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/WebApp/V1/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="11_F25DC773A252ABDACC10484FB9DE559E5ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51F78811-44DC-4926-8BED-9DA71121E038}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="11_F25DC773A252ABDACC10484FB9DE559E5ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AAE350F-DAC2-4143-B86F-FD0CC13CCCE8}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="49">
   <si>
     <t>香蕉</t>
   </si>
@@ -276,6 +276,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1033,9 +1037,21 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/WebApp/V1/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="11_F25DC773A252ABDACC10484FB9DE559E5ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AAE350F-DAC2-4143-B86F-FD0CC13CCCE8}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="11_F25DC773A252ABDACC10484FB9DE559E5ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C0EF8BF-62B9-41DC-A044-0EBE3025DA0E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="48">
   <si>
     <t>香蕉</t>
   </si>
@@ -155,9 +155,6 @@
   </si>
   <si>
     <t>白云</t>
-  </si>
-  <si>
-    <t>受伤</t>
   </si>
   <si>
     <t>手上</t>
@@ -989,7 +986,7 @@
         <v>35</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="27" x14ac:dyDescent="0.45">
@@ -1022,7 +1019,7 @@
         <v>44</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -1030,27 +1027,24 @@
         <v>39</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B7" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="C7" s="4"/>
     </row>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/WebApp/V1/content/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c72363082c40911d/doc/WXiao/web app/CodeM/content/0317 wx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="11_F25DC773A252ABDACC10484FB9DE559E5ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C0EF8BF-62B9-41DC-A044-0EBE3025DA0E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC237AD6-B158-4F97-BB6E-780A0A77F173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="86">
   <si>
     <t>香蕉</t>
   </si>
@@ -43,57 +43,9 @@
     <t>老师</t>
   </si>
   <si>
-    <t>谢谢</t>
-  </si>
-  <si>
     <t>你好</t>
   </si>
   <si>
-    <t>对不起</t>
-  </si>
-  <si>
-    <t>二</t>
-  </si>
-  <si>
-    <t>三</t>
-  </si>
-  <si>
-    <t>四</t>
-  </si>
-  <si>
-    <t>五</t>
-  </si>
-  <si>
-    <t>六</t>
-  </si>
-  <si>
-    <t>七</t>
-  </si>
-  <si>
-    <t>八</t>
-  </si>
-  <si>
-    <t>九</t>
-  </si>
-  <si>
-    <t>十</t>
-  </si>
-  <si>
-    <t>十一</t>
-  </si>
-  <si>
-    <t>十二</t>
-  </si>
-  <si>
-    <t>十三</t>
-  </si>
-  <si>
-    <t>十四</t>
-  </si>
-  <si>
-    <t>十五</t>
-  </si>
-  <si>
     <t>十六</t>
   </si>
   <si>
@@ -109,9 +61,6 @@
     <t>二十</t>
   </si>
   <si>
-    <t>一</t>
-  </si>
-  <si>
     <t>an</t>
   </si>
   <si>
@@ -170,6 +119,171 @@
   </si>
   <si>
     <t>Round3</t>
+  </si>
+  <si>
+    <t>大王</t>
+  </si>
+  <si>
+    <t>雪对风</t>
+  </si>
+  <si>
+    <t>鹅鹅鹅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鱼儿的家   </t>
+  </si>
+  <si>
+    <t>我</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鸟对虫  </t>
+  </si>
+  <si>
+    <t>云对雨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">土地  </t>
+  </si>
+  <si>
+    <t>白毛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">树上的花 </t>
+  </si>
+  <si>
+    <t>绿水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天上有云 </t>
+  </si>
+  <si>
+    <t>树林是小鸟的家</t>
+  </si>
+  <si>
+    <t>jia</t>
+  </si>
+  <si>
+    <t>自云</t>
+  </si>
+  <si>
+    <t>百云</t>
+  </si>
+  <si>
+    <t>虹花</t>
+  </si>
+  <si>
+    <t>虹化</t>
+  </si>
+  <si>
+    <t>毛毛中</t>
+  </si>
+  <si>
+    <t>毛毛忠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天鹅  </t>
+  </si>
+  <si>
+    <t>天鸭</t>
+  </si>
+  <si>
+    <t>天鹰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我家 </t>
+  </si>
+  <si>
+    <t>找家</t>
+  </si>
+  <si>
+    <t>庄家</t>
+  </si>
+  <si>
+    <t xml:space="preserve">王子 </t>
+  </si>
+  <si>
+    <t>玉子</t>
+  </si>
+  <si>
+    <t>主子</t>
+  </si>
+  <si>
+    <t>鱼儿</t>
+  </si>
+  <si>
+    <t>昌儿</t>
+  </si>
+  <si>
+    <t>田儿</t>
+  </si>
+  <si>
+    <t xml:space="preserve">树林  </t>
+  </si>
+  <si>
+    <t>树木</t>
+  </si>
+  <si>
+    <t>森林</t>
+  </si>
+  <si>
+    <t>是的</t>
+  </si>
+  <si>
+    <t>有的</t>
+  </si>
+  <si>
+    <t>对的</t>
+  </si>
+  <si>
+    <t>木头</t>
+  </si>
+  <si>
+    <t>大头</t>
+  </si>
+  <si>
+    <t>木达</t>
+  </si>
+  <si>
+    <t>几个</t>
+  </si>
+  <si>
+    <t>九个</t>
+  </si>
+  <si>
+    <t>叽个</t>
+  </si>
+  <si>
+    <t>下雨</t>
+  </si>
+  <si>
+    <t>下雪</t>
+  </si>
+  <si>
+    <t>下霜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对了  </t>
+  </si>
+  <si>
+    <t>村子</t>
+  </si>
+  <si>
+    <t>对子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大风 </t>
+  </si>
+  <si>
+    <t>大月</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 小鸟</t>
+  </si>
+  <si>
+    <t>小岛</t>
+  </si>
+  <si>
+    <t>小鸡</t>
   </si>
 </sst>
 </file>
@@ -273,10 +387,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -543,40 +653,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -585,18 +695,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -605,18 +715,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>5</v>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -625,18 +735,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>3</v>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -645,18 +755,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>3</v>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
+        <v>54</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -665,18 +775,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>6</v>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
+        <v>59</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -685,18 +795,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>1</v>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -705,18 +815,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>65</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -725,18 +835,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>5</v>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -745,18 +855,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>3</v>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -765,18 +875,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>3</v>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>72</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -785,18 +895,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>6</v>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>75</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -805,18 +915,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>1</v>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>78</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -825,18 +935,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>4</v>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>82</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -845,18 +955,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>5</v>
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" t="s">
+        <v>85</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -865,12 +975,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>0</v>
@@ -885,12 +995,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>2</v>
@@ -905,18 +1015,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -925,12 +1035,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>0</v>
@@ -945,12 +1055,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>2</v>
@@ -972,95 +1082,154 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="9.06640625" style="5"/>
+    <col min="1" max="1" width="16.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="27" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C7" s="4"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c72363082c40911d/doc/WXiao/web app/CodeM/content/0317 wx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC237AD6-B158-4F97-BB6E-780A0A77F173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C289C44D-1DFF-41AC-9F0B-B78E669B79BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,40 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="86">
-  <si>
-    <t>香蕉</t>
-  </si>
-  <si>
-    <t>西瓜</t>
-  </si>
-  <si>
-    <t>医生</t>
-  </si>
-  <si>
-    <t>护士</t>
-  </si>
-  <si>
-    <t>老师</t>
-  </si>
-  <si>
-    <t>你好</t>
-  </si>
-  <si>
-    <t>十六</t>
-  </si>
-  <si>
-    <t>十七</t>
-  </si>
-  <si>
-    <t>十八</t>
-  </si>
-  <si>
-    <t>十九</t>
-  </si>
-  <si>
-    <t>二十</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="114">
   <si>
     <t>an</t>
   </si>
@@ -284,6 +251,123 @@
   </si>
   <si>
     <t>小鸡</t>
+  </si>
+  <si>
+    <t>用来</t>
+  </si>
+  <si>
+    <t>国来</t>
+  </si>
+  <si>
+    <t>用米</t>
+  </si>
+  <si>
+    <t>妈妈</t>
+  </si>
+  <si>
+    <t>妈马</t>
+  </si>
+  <si>
+    <t>马马</t>
+  </si>
+  <si>
+    <t>毛巾</t>
+  </si>
+  <si>
+    <t>手币</t>
+  </si>
+  <si>
+    <t>毛币</t>
+  </si>
+  <si>
+    <t>白马</t>
+  </si>
+  <si>
+    <t>目马</t>
+  </si>
+  <si>
+    <t>木马</t>
+  </si>
+  <si>
+    <t>冲水</t>
+  </si>
+  <si>
+    <t>中水</t>
+  </si>
+  <si>
+    <t>虫水</t>
+  </si>
+  <si>
+    <t>用力</t>
+  </si>
+  <si>
+    <t>用刀</t>
+  </si>
+  <si>
+    <t>用刁</t>
+  </si>
+  <si>
+    <t>一边</t>
+  </si>
+  <si>
+    <t>一力</t>
+  </si>
+  <si>
+    <t>一会</t>
+  </si>
+  <si>
+    <t>鱼几</t>
+  </si>
+  <si>
+    <t>色儿</t>
+  </si>
+  <si>
+    <t>我家</t>
+  </si>
+  <si>
+    <t>白的</t>
+  </si>
+  <si>
+    <t>走的</t>
+  </si>
+  <si>
+    <t>我屋</t>
+  </si>
+  <si>
+    <t>绿树</t>
+  </si>
+  <si>
+    <t>树林</t>
+  </si>
+  <si>
+    <t>对林</t>
+  </si>
+  <si>
+    <t>几人</t>
+  </si>
+  <si>
+    <t>几入</t>
+  </si>
+  <si>
+    <t>几八</t>
+  </si>
+  <si>
+    <t>儿子</t>
+  </si>
+  <si>
+    <t>几子</t>
+  </si>
+  <si>
+    <t>凡子</t>
+  </si>
+  <si>
+    <t>我去了</t>
+  </si>
+  <si>
+    <t>鹅去了</t>
+  </si>
+  <si>
+    <t>鸟去了</t>
   </si>
 </sst>
 </file>
@@ -319,27 +403,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -361,17 +430,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -652,41 +718,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -695,18 +761,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -715,18 +781,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -735,18 +801,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -755,18 +821,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -775,18 +841,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -795,18 +861,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -815,18 +881,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -835,18 +901,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -855,18 +921,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -875,18 +941,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -895,18 +961,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -915,18 +981,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -935,18 +1001,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -955,18 +1021,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -975,104 +1041,214 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17">
-        <v>16</v>
-      </c>
-      <c r="F17">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18">
-        <v>17</v>
-      </c>
-      <c r="F18">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19">
-        <v>18</v>
-      </c>
-      <c r="F19">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>19</v>
-      </c>
-      <c r="F20">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21">
-        <v>20</v>
-      </c>
-      <c r="F21">
-        <v>21</v>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1083,151 +1259,151 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="5"/>
+    <col min="1" max="1" width="16.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="3" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="3" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B16" t="s">
         <v>31</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
         <v>32</v>
-      </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>43</v>
       </c>
       <c r="B17"/>
     </row>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C289C44D-1DFF-41AC-9F0B-B78E669B79BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4A6AC3-1202-4162-8304-BA1D5EE7374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="161">
   <si>
     <t>an</t>
   </si>
@@ -368,6 +368,147 @@
   </si>
   <si>
     <t>鸟去了</t>
+  </si>
+  <si>
+    <t>鱼片</t>
+  </si>
+  <si>
+    <t>田片</t>
+  </si>
+  <si>
+    <t>鱼力</t>
+  </si>
+  <si>
+    <t>雪花</t>
+  </si>
+  <si>
+    <t>雨花</t>
+  </si>
+  <si>
+    <t>雪化</t>
+  </si>
+  <si>
+    <t>无人</t>
+  </si>
+  <si>
+    <t>天人</t>
+  </si>
+  <si>
+    <t>无入</t>
+  </si>
+  <si>
+    <t>不见</t>
+  </si>
+  <si>
+    <t>下见</t>
+  </si>
+  <si>
+    <t>不贝</t>
+  </si>
+  <si>
+    <t>八边</t>
+  </si>
+  <si>
+    <t>入边</t>
+  </si>
+  <si>
+    <t>八力</t>
+  </si>
+  <si>
+    <t>飞入</t>
+  </si>
+  <si>
+    <t>飞人</t>
+  </si>
+  <si>
+    <t>飞八</t>
+  </si>
+  <si>
+    <t>儿了</t>
+  </si>
+  <si>
+    <t>冲冰</t>
+  </si>
+  <si>
+    <t>甩力</t>
+  </si>
+  <si>
+    <t>白鸟</t>
+  </si>
+  <si>
+    <t>白妈</t>
+  </si>
+  <si>
+    <t>来去</t>
+  </si>
+  <si>
+    <t>来云</t>
+  </si>
+  <si>
+    <t>米去</t>
+  </si>
+  <si>
+    <t>手巾</t>
+  </si>
+  <si>
+    <t>毛布</t>
+  </si>
+  <si>
+    <t>鹅家</t>
+  </si>
+  <si>
+    <t>是白</t>
+  </si>
+  <si>
+    <t>禾马</t>
+  </si>
+  <si>
+    <t>本马</t>
+  </si>
+  <si>
+    <t>天鹅</t>
+  </si>
+  <si>
+    <t>大鹅</t>
+  </si>
+  <si>
+    <t>太鹅</t>
+  </si>
+  <si>
+    <t>鱼儿不见了</t>
+  </si>
+  <si>
+    <t>无力</t>
+  </si>
+  <si>
+    <t>八片鹅毛</t>
+  </si>
+  <si>
+    <t>飞鸟入树林</t>
+  </si>
+  <si>
+    <t>山上的红花</t>
+  </si>
+  <si>
+    <t>雨雪风云</t>
+  </si>
+  <si>
+    <t>儿子对了</t>
+  </si>
+  <si>
+    <t>水边的家</t>
+  </si>
+  <si>
+    <t>用来冲冲手</t>
+  </si>
+  <si>
+    <t>妈妈不是马马</t>
+  </si>
+  <si>
+    <t>红毛巾</t>
+  </si>
+  <si>
+    <t>白天</t>
   </si>
 </sst>
 </file>
@@ -718,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -1249,6 +1390,244 @@
       </c>
       <c r="D33" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>87</v>
+      </c>
+      <c r="B43" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>137</v>
+      </c>
+      <c r="B46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>98</v>
+      </c>
+      <c r="B48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" t="s">
+        <v>86</v>
+      </c>
+      <c r="C51" t="s">
+        <v>144</v>
+      </c>
+      <c r="D51" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>146</v>
+      </c>
+      <c r="B52" t="s">
+        <v>147</v>
+      </c>
+      <c r="C52" t="s">
+        <v>148</v>
+      </c>
+      <c r="D52" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.1328125" style="4" bestFit="1" customWidth="1"/>
@@ -1407,6 +1786,66 @@
       </c>
       <c r="B17"/>
     </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4A6AC3-1202-4162-8304-BA1D5EE7374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -484,9 +484,6 @@
     <t>八片鹅毛</t>
   </si>
   <si>
-    <t>飞鸟入树林</t>
-  </si>
-  <si>
     <t>山上的红花</t>
   </si>
   <si>
@@ -499,9 +496,6 @@
     <t>水边的家</t>
   </si>
   <si>
-    <t>用来冲冲手</t>
-  </si>
-  <si>
     <t>妈妈不是马马</t>
   </si>
   <si>
@@ -509,6 +503,12 @@
   </si>
   <si>
     <t>白天</t>
+  </si>
+  <si>
+    <t>飞鸟入林</t>
+  </si>
+  <si>
+    <t>用来冲冲水</t>
   </si>
 </sst>
 </file>
@@ -1637,11 +1637,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="4" customWidth="1"/>
     <col min="3" max="3" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1788,62 +1788,50 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
         <v>149</v>
       </c>
+      <c r="B25" s="4" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A28" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A30" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A31" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A32" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B0703B-F44B-4C94-A196-9F3C00A2AA08}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="209">
   <si>
     <t>an</t>
   </si>
@@ -509,6 +509,150 @@
   </si>
   <si>
     <t>用来冲冲水</t>
+  </si>
+  <si>
+    <t>月儿</t>
+  </si>
+  <si>
+    <t>月几</t>
+  </si>
+  <si>
+    <t>朋儿</t>
+  </si>
+  <si>
+    <t>《月儿弯弯》</t>
+  </si>
+  <si>
+    <t>青山</t>
+  </si>
+  <si>
+    <t>月山</t>
+  </si>
+  <si>
+    <t>青出</t>
+  </si>
+  <si>
+    <t>挂上去</t>
+  </si>
+  <si>
+    <t>挂下去</t>
+  </si>
+  <si>
+    <t>挂上云</t>
+  </si>
+  <si>
+    <t>出去</t>
+  </si>
+  <si>
+    <t>山去</t>
+  </si>
+  <si>
+    <t>出云</t>
+  </si>
+  <si>
+    <t>河水</t>
+  </si>
+  <si>
+    <t>可水</t>
+  </si>
+  <si>
+    <t>河冰</t>
+  </si>
+  <si>
+    <t>小虫子</t>
+  </si>
+  <si>
+    <t>小中子</t>
+  </si>
+  <si>
+    <t>小虫了</t>
+  </si>
+  <si>
+    <t>大雪</t>
+  </si>
+  <si>
+    <t>天雪</t>
+  </si>
+  <si>
+    <t>大雨</t>
+  </si>
+  <si>
+    <t>花园</t>
+  </si>
+  <si>
+    <t>花圆</t>
+  </si>
+  <si>
+    <t>花元</t>
+  </si>
+  <si>
+    <t>家园</t>
+  </si>
+  <si>
+    <t>家圆</t>
+  </si>
+  <si>
+    <t>家元</t>
+  </si>
+  <si>
+    <t>鱼丁</t>
+  </si>
+  <si>
+    <t>无八</t>
+  </si>
+  <si>
+    <t>飞鸟</t>
+  </si>
+  <si>
+    <t>飞鹅</t>
+  </si>
+  <si>
+    <t>飞鸡</t>
+  </si>
+  <si>
+    <t>入水</t>
+  </si>
+  <si>
+    <t>人水</t>
+  </si>
+  <si>
+    <t>八水</t>
+  </si>
+  <si>
+    <t>冲手</t>
+  </si>
+  <si>
+    <t>冲毛</t>
+  </si>
+  <si>
+    <t>中手</t>
+  </si>
+  <si>
+    <t>不见了</t>
+  </si>
+  <si>
+    <t>不贝了</t>
+  </si>
+  <si>
+    <t>下见了</t>
+  </si>
+  <si>
+    <t>风风雨雨</t>
+  </si>
+  <si>
+    <t>凤凤雨雨</t>
+  </si>
+  <si>
+    <t>风风雨雪</t>
+  </si>
+  <si>
+    <t>树林边</t>
+  </si>
+  <si>
+    <t>树木边</t>
+  </si>
+  <si>
+    <t>树林力</t>
   </si>
 </sst>
 </file>
@@ -859,8 +1003,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="12.53125" customWidth="1"/>
+    <col min="5" max="5" width="18.1328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -1574,7 +1722,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1588,7 +1736,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>103</v>
       </c>
@@ -1602,7 +1750,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>86</v>
       </c>
@@ -1616,7 +1764,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>146</v>
       </c>
@@ -1628,6 +1776,263 @@
       </c>
       <c r="D52" t="s">
         <v>146</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E54" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" t="s">
+        <v>163</v>
+      </c>
+      <c r="D55" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>165</v>
+      </c>
+      <c r="B56" t="s">
+        <v>165</v>
+      </c>
+      <c r="C56" t="s">
+        <v>166</v>
+      </c>
+      <c r="D56" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>168</v>
+      </c>
+      <c r="B57" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" t="s">
+        <v>170</v>
+      </c>
+      <c r="D57" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>171</v>
+      </c>
+      <c r="B58" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" t="s">
+        <v>171</v>
+      </c>
+      <c r="D58" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>174</v>
+      </c>
+      <c r="B59" t="s">
+        <v>175</v>
+      </c>
+      <c r="C59" t="s">
+        <v>176</v>
+      </c>
+      <c r="D59" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>177</v>
+      </c>
+      <c r="B60" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" t="s">
+        <v>177</v>
+      </c>
+      <c r="D60" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>180</v>
+      </c>
+      <c r="B61" t="s">
+        <v>180</v>
+      </c>
+      <c r="C61" t="s">
+        <v>181</v>
+      </c>
+      <c r="D61" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>183</v>
+      </c>
+      <c r="B62" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>114</v>
+      </c>
+      <c r="B64" t="s">
+        <v>115</v>
+      </c>
+      <c r="C64" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>120</v>
+      </c>
+      <c r="B65" t="s">
+        <v>190</v>
+      </c>
+      <c r="C65" t="s">
+        <v>122</v>
+      </c>
+      <c r="D65" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>191</v>
+      </c>
+      <c r="B66" t="s">
+        <v>192</v>
+      </c>
+      <c r="C66" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>194</v>
+      </c>
+      <c r="B67" t="s">
+        <v>194</v>
+      </c>
+      <c r="C67" t="s">
+        <v>195</v>
+      </c>
+      <c r="D67" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>197</v>
+      </c>
+      <c r="B68" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68" t="s">
+        <v>199</v>
+      </c>
+      <c r="D68" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>200</v>
+      </c>
+      <c r="B69" t="s">
+        <v>201</v>
+      </c>
+      <c r="C69" t="s">
+        <v>200</v>
+      </c>
+      <c r="D69" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>81</v>
+      </c>
+      <c r="B70" t="s">
+        <v>140</v>
+      </c>
+      <c r="C70" t="s">
+        <v>83</v>
+      </c>
+      <c r="D70" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>203</v>
+      </c>
+      <c r="B71" t="s">
+        <v>204</v>
+      </c>
+      <c r="C71" t="s">
+        <v>205</v>
+      </c>
+      <c r="D71" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>206</v>
+      </c>
+      <c r="B72" t="s">
+        <v>207</v>
+      </c>
+      <c r="C72" t="s">
+        <v>206</v>
+      </c>
+      <c r="D72" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B0703B-F44B-4C94-A196-9F3C00A2AA08}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BDBAEC3-1C16-48DD-AD9C-4F37CD4E51B4}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="211">
   <si>
     <t>an</t>
   </si>
@@ -653,6 +653,12 @@
   </si>
   <si>
     <t>树林力</t>
+  </si>
+  <si>
+    <t>《洗手歌》</t>
+  </si>
+  <si>
+    <t>eee</t>
   </si>
 </sst>
 </file>
@@ -738,6 +744,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1330,7 +1340,38 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" t="s">
+        <v>209</v>
+      </c>
+      <c r="D17" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C18" t="s">
+        <v>209</v>
+      </c>
+      <c r="D18" t="s">
+        <v>209</v>
+      </c>
+      <c r="E18" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>75</v>
       </c>
@@ -1344,7 +1385,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>78</v>
       </c>
@@ -1358,7 +1399,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -1372,7 +1413,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>86</v>
       </c>
@@ -1386,7 +1427,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>87</v>
       </c>
@@ -1400,7 +1441,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>90</v>
       </c>
@@ -1414,7 +1455,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>93</v>
       </c>
@@ -1428,7 +1469,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -1442,7 +1483,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1456,7 +1497,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -1470,7 +1511,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -1484,7 +1525,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>103</v>
       </c>
@@ -1498,7 +1539,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -1512,7 +1553,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>108</v>
       </c>
@@ -1540,6 +1581,34 @@
         <v>113</v>
       </c>
     </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>210</v>
+      </c>
+      <c r="B34" t="s">
+        <v>210</v>
+      </c>
+      <c r="C34" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>210</v>
+      </c>
+      <c r="B35" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D35" t="s">
+        <v>210</v>
+      </c>
+    </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>114</v>
@@ -1778,7 +1847,33 @@
         <v>146</v>
       </c>
     </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>164</v>
+      </c>
+      <c r="B53" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53" t="s">
+        <v>164</v>
+      </c>
+    </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>164</v>
+      </c>
+      <c r="B54" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54" t="s">
+        <v>164</v>
+      </c>
+      <c r="D54" t="s">
+        <v>164</v>
+      </c>
       <c r="E54" t="s">
         <v>164</v>
       </c>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BDBAEC3-1C16-48DD-AD9C-4F37CD4E51B4}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30931B4C-9943-4CA4-8792-37D36AA7CB3D}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="246">
   <si>
     <t>an</t>
   </si>
@@ -127,9 +127,6 @@
     <t>树林是小鸟的家</t>
   </si>
   <si>
-    <t>jia</t>
-  </si>
-  <si>
     <t>自云</t>
   </si>
   <si>
@@ -659,6 +656,114 @@
   </si>
   <si>
     <t>eee</t>
+  </si>
+  <si>
+    <t>《四是四》</t>
+  </si>
+  <si>
+    <t>口令</t>
+  </si>
+  <si>
+    <t>口今</t>
+  </si>
+  <si>
+    <t>日令</t>
+  </si>
+  <si>
+    <t>四天</t>
+  </si>
+  <si>
+    <t>四大</t>
+  </si>
+  <si>
+    <t>四夫</t>
+  </si>
+  <si>
+    <t>十八</t>
+  </si>
+  <si>
+    <t>十人</t>
+  </si>
+  <si>
+    <t>十入</t>
+  </si>
+  <si>
+    <t>飞乌</t>
+  </si>
+  <si>
+    <t>宝贝</t>
+  </si>
+  <si>
+    <t>宝见</t>
+  </si>
+  <si>
+    <t>宝页</t>
+  </si>
+  <si>
+    <t>杯子</t>
+  </si>
+  <si>
+    <t>杯了</t>
+  </si>
+  <si>
+    <t>林子</t>
+  </si>
+  <si>
+    <t>比一比</t>
+  </si>
+  <si>
+    <t>北一北</t>
+  </si>
+  <si>
+    <t>此一此</t>
+  </si>
+  <si>
+    <t>日几</t>
+  </si>
+  <si>
+    <t>清出</t>
+  </si>
+  <si>
+    <t>挂毛巾</t>
+  </si>
+  <si>
+    <t>挂手巾</t>
+  </si>
+  <si>
+    <t>挂毛币</t>
+  </si>
+  <si>
+    <t>海水</t>
+  </si>
+  <si>
+    <t>十四不是四十</t>
+  </si>
+  <si>
+    <t>四是四十是十</t>
+  </si>
+  <si>
+    <t>小河弯弯出青山</t>
+  </si>
+  <si>
+    <t>飞入水中不见了</t>
+  </si>
+  <si>
+    <t>用水来冲手</t>
+  </si>
+  <si>
+    <t>大鹅来了我家</t>
+  </si>
+  <si>
+    <t>雪对风鸟对虫</t>
+  </si>
+  <si>
+    <t>月儿挂青天</t>
+  </si>
+  <si>
+    <t>鱼妈妈的儿子</t>
+  </si>
+  <si>
+    <t>《家》</t>
   </si>
 </sst>
 </file>
@@ -1013,10 +1118,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.53125" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="16.86328125" customWidth="1"/>
+    <col min="4" max="4" width="21.1328125" customWidth="1"/>
     <col min="5" max="5" width="18.1328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1048,10 +1156,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
         <v>34</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1065,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1085,13 +1193,13 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1102,16 +1210,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>41</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1122,16 +1230,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
         <v>43</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1142,16 +1250,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
         <v>46</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
         <v>47</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>48</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1162,16 +1270,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>50</v>
-      </c>
-      <c r="D8" t="s">
-        <v>51</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1182,16 +1290,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
         <v>52</v>
       </c>
-      <c r="B9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>53</v>
-      </c>
-      <c r="D9" t="s">
-        <v>54</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1202,16 +1310,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
         <v>55</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>56</v>
       </c>
-      <c r="C10" t="s">
-        <v>57</v>
-      </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1222,16 +1330,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
         <v>58</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
         <v>59</v>
-      </c>
-      <c r="C11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1242,16 +1350,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
         <v>61</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>62</v>
       </c>
-      <c r="C12" t="s">
-        <v>63</v>
-      </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1262,16 +1370,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" t="s">
         <v>64</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>65</v>
       </c>
-      <c r="C13" t="s">
-        <v>66</v>
-      </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1282,16 +1390,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" t="s">
         <v>67</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>68</v>
       </c>
-      <c r="C14" t="s">
-        <v>69</v>
-      </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1302,16 +1410,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
         <v>70</v>
-      </c>
-      <c r="B15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" t="s">
-        <v>71</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1322,16 +1430,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" t="s">
         <v>72</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" t="s">
         <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" t="s">
-        <v>74</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1342,792 +1450,1016 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
         <v>75</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>76</v>
       </c>
-      <c r="C19" t="s">
-        <v>77</v>
-      </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" t="s">
         <v>78</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" t="s">
         <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" t="s">
         <v>81</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>82</v>
       </c>
-      <c r="C21" t="s">
-        <v>83</v>
-      </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
         <v>84</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>85</v>
-      </c>
-      <c r="D22" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" t="s">
         <v>87</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" t="s">
         <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" t="s">
         <v>90</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>91</v>
       </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s">
         <v>93</v>
       </c>
-      <c r="B25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>94</v>
-      </c>
-      <c r="D25" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s">
         <v>96</v>
       </c>
-      <c r="C26" t="s">
-        <v>97</v>
-      </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" t="s">
         <v>99</v>
-      </c>
-      <c r="D27" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" t="s">
         <v>102</v>
-      </c>
-      <c r="C29" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" t="s">
         <v>103</v>
       </c>
-      <c r="B30" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" t="s">
-        <v>104</v>
-      </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" t="s">
         <v>105</v>
       </c>
-      <c r="B31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>106</v>
-      </c>
-      <c r="D31" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" t="s">
         <v>108</v>
       </c>
-      <c r="B32" t="s">
-        <v>110</v>
-      </c>
-      <c r="C32" t="s">
-        <v>109</v>
-      </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" t="s">
         <v>111</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" t="s">
         <v>112</v>
-      </c>
-      <c r="C33" t="s">
-        <v>111</v>
-      </c>
-      <c r="D33" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B34" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C34" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D34" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" t="s">
         <v>114</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>115</v>
       </c>
-      <c r="C36" t="s">
-        <v>116</v>
-      </c>
       <c r="D36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" t="s">
         <v>117</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" t="s">
         <v>118</v>
-      </c>
-      <c r="C37" t="s">
-        <v>117</v>
-      </c>
-      <c r="D37" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" t="s">
         <v>120</v>
       </c>
-      <c r="B38" t="s">
-        <v>120</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>121</v>
-      </c>
-      <c r="D38" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" t="s">
         <v>123</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>124</v>
       </c>
-      <c r="C39" t="s">
-        <v>125</v>
-      </c>
       <c r="D39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
+        <v>125</v>
+      </c>
+      <c r="B40" t="s">
         <v>126</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" t="s">
         <v>127</v>
-      </c>
-      <c r="C40" t="s">
-        <v>126</v>
-      </c>
-      <c r="D40" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" t="s">
         <v>129</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>130</v>
       </c>
-      <c r="C41" t="s">
-        <v>131</v>
-      </c>
       <c r="D41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" t="s">
         <v>108</v>
       </c>
-      <c r="B42" t="s">
-        <v>109</v>
-      </c>
       <c r="C42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D43" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44" t="s">
         <v>90</v>
       </c>
-      <c r="B44" t="s">
-        <v>91</v>
-      </c>
       <c r="C44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" t="s">
         <v>135</v>
-      </c>
-      <c r="C45" t="s">
-        <v>84</v>
-      </c>
-      <c r="D45" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" t="s">
         <v>137</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
+        <v>136</v>
+      </c>
+      <c r="D46" t="s">
         <v>138</v>
-      </c>
-      <c r="C46" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C47" t="s">
+        <v>139</v>
+      </c>
+      <c r="D47" t="s">
         <v>140</v>
-      </c>
-      <c r="D47" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B50" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" t="s">
         <v>103</v>
       </c>
-      <c r="B50" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" t="s">
-        <v>104</v>
-      </c>
       <c r="D50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C51" t="s">
+        <v>143</v>
+      </c>
+      <c r="D51" t="s">
         <v>144</v>
-      </c>
-      <c r="D51" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
+        <v>145</v>
+      </c>
+      <c r="B52" t="s">
         <v>146</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>147</v>
       </c>
-      <c r="C52" t="s">
-        <v>148</v>
-      </c>
       <c r="D52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B53" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C53" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D53" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" t="s">
         <v>161</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>162</v>
       </c>
-      <c r="C55" t="s">
-        <v>163</v>
-      </c>
       <c r="D55" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56" t="s">
         <v>165</v>
       </c>
-      <c r="B56" t="s">
-        <v>165</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>166</v>
-      </c>
-      <c r="D56" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" t="s">
         <v>168</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>169</v>
       </c>
-      <c r="C57" t="s">
-        <v>170</v>
-      </c>
       <c r="D57" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
+        <v>170</v>
+      </c>
+      <c r="B58" t="s">
         <v>171</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
+        <v>170</v>
+      </c>
+      <c r="D58" t="s">
         <v>172</v>
-      </c>
-      <c r="C58" t="s">
-        <v>171</v>
-      </c>
-      <c r="D58" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
+        <v>173</v>
+      </c>
+      <c r="B59" t="s">
         <v>174</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>175</v>
       </c>
-      <c r="C59" t="s">
-        <v>176</v>
-      </c>
       <c r="D59" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" t="s">
         <v>177</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
+        <v>176</v>
+      </c>
+      <c r="D60" t="s">
         <v>178</v>
-      </c>
-      <c r="C60" t="s">
-        <v>177</v>
-      </c>
-      <c r="D60" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
+        <v>179</v>
+      </c>
+      <c r="B61" t="s">
+        <v>179</v>
+      </c>
+      <c r="C61" t="s">
         <v>180</v>
       </c>
-      <c r="B61" t="s">
-        <v>180</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>181</v>
-      </c>
-      <c r="D61" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" t="s">
         <v>183</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>184</v>
       </c>
-      <c r="C62" t="s">
-        <v>185</v>
-      </c>
       <c r="D62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
+        <v>185</v>
+      </c>
+      <c r="B63" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63" t="s">
         <v>186</v>
       </c>
-      <c r="B63" t="s">
-        <v>186</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>187</v>
-      </c>
-      <c r="D63" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
+        <v>113</v>
+      </c>
+      <c r="B64" t="s">
         <v>114</v>
       </c>
-      <c r="B64" t="s">
-        <v>115</v>
-      </c>
       <c r="C64" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D64" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B65" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D65" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
+        <v>190</v>
+      </c>
+      <c r="B66" t="s">
         <v>191</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
+        <v>190</v>
+      </c>
+      <c r="D66" t="s">
         <v>192</v>
-      </c>
-      <c r="C66" t="s">
-        <v>191</v>
-      </c>
-      <c r="D66" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
+        <v>193</v>
+      </c>
+      <c r="B67" t="s">
+        <v>193</v>
+      </c>
+      <c r="C67" t="s">
         <v>194</v>
       </c>
-      <c r="B67" t="s">
-        <v>194</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>195</v>
-      </c>
-      <c r="D67" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
+        <v>196</v>
+      </c>
+      <c r="B68" t="s">
         <v>197</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>198</v>
       </c>
-      <c r="C68" t="s">
-        <v>199</v>
-      </c>
       <c r="D68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
+        <v>199</v>
+      </c>
+      <c r="B69" t="s">
         <v>200</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
+        <v>199</v>
+      </c>
+      <c r="D69" t="s">
         <v>201</v>
-      </c>
-      <c r="C69" t="s">
-        <v>200</v>
-      </c>
-      <c r="D69" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C70" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D70" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
+        <v>202</v>
+      </c>
+      <c r="B71" t="s">
         <v>203</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>204</v>
       </c>
-      <c r="C71" t="s">
-        <v>205</v>
-      </c>
       <c r="D71" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
+        <v>205</v>
+      </c>
+      <c r="B72" t="s">
         <v>206</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
+        <v>205</v>
+      </c>
+      <c r="D72" t="s">
         <v>207</v>
       </c>
-      <c r="C72" t="s">
-        <v>206</v>
-      </c>
-      <c r="D72" t="s">
-        <v>208</v>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>210</v>
+      </c>
+      <c r="B73" t="s">
+        <v>210</v>
+      </c>
+      <c r="C73" t="s">
+        <v>210</v>
+      </c>
+      <c r="D73" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>211</v>
+      </c>
+      <c r="B74" t="s">
+        <v>211</v>
+      </c>
+      <c r="C74" t="s">
+        <v>212</v>
+      </c>
+      <c r="D74" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>214</v>
+      </c>
+      <c r="B75" t="s">
+        <v>215</v>
+      </c>
+      <c r="C75" t="s">
+        <v>216</v>
+      </c>
+      <c r="D75" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>217</v>
+      </c>
+      <c r="B76" t="s">
+        <v>217</v>
+      </c>
+      <c r="C76" t="s">
+        <v>218</v>
+      </c>
+      <c r="D76" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>190</v>
+      </c>
+      <c r="B77" t="s">
+        <v>220</v>
+      </c>
+      <c r="C77" t="s">
+        <v>190</v>
+      </c>
+      <c r="D77" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>221</v>
+      </c>
+      <c r="B78" t="s">
+        <v>221</v>
+      </c>
+      <c r="C78" t="s">
+        <v>222</v>
+      </c>
+      <c r="D78" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>224</v>
+      </c>
+      <c r="B79" t="s">
+        <v>225</v>
+      </c>
+      <c r="C79" t="s">
+        <v>226</v>
+      </c>
+      <c r="D79" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>227</v>
+      </c>
+      <c r="B80" t="s">
+        <v>227</v>
+      </c>
+      <c r="C80" t="s">
+        <v>228</v>
+      </c>
+      <c r="D80" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" t="s">
+        <v>230</v>
+      </c>
+      <c r="C81" t="s">
+        <v>160</v>
+      </c>
+      <c r="D81" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>164</v>
+      </c>
+      <c r="B82" t="s">
+        <v>166</v>
+      </c>
+      <c r="C82" t="s">
+        <v>231</v>
+      </c>
+      <c r="D82" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>232</v>
+      </c>
+      <c r="B83" t="s">
+        <v>233</v>
+      </c>
+      <c r="C83" t="s">
+        <v>232</v>
+      </c>
+      <c r="D83" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>170</v>
+      </c>
+      <c r="B84" t="s">
+        <v>171</v>
+      </c>
+      <c r="C84" t="s">
+        <v>172</v>
+      </c>
+      <c r="D84" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>173</v>
+      </c>
+      <c r="B85" t="s">
+        <v>173</v>
+      </c>
+      <c r="C85" t="s">
+        <v>174</v>
+      </c>
+      <c r="D85" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>182</v>
+      </c>
+      <c r="B86" t="s">
+        <v>184</v>
+      </c>
+      <c r="C86" t="s">
+        <v>182</v>
+      </c>
+      <c r="D86" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>74</v>
+      </c>
+      <c r="B87" t="s">
+        <v>76</v>
+      </c>
+      <c r="C87" t="s">
+        <v>75</v>
+      </c>
+      <c r="D87" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>199</v>
+      </c>
+      <c r="B88" t="s">
+        <v>200</v>
+      </c>
+      <c r="C88" t="s">
+        <v>199</v>
+      </c>
+      <c r="D88" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2137,7 +2469,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.1328125" style="4" bestFit="1" customWidth="1"/>
@@ -2237,7 +2569,7 @@
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
@@ -2280,58 +2612,101 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>32</v>
       </c>
       <c r="B17"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B22" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" s="4" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>160</v>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="171" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30931B4C-9943-4CA4-8792-37D36AA7CB3D}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{113C0928-7D5A-4257-984C-AAC657BCBC39}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -739,9 +739,6 @@
     <t>十四不是四十</t>
   </si>
   <si>
-    <t>四是四十是十</t>
-  </si>
-  <si>
     <t>小河弯弯出青山</t>
   </si>
   <si>
@@ -751,12 +748,6 @@
     <t>用水来冲手</t>
   </si>
   <si>
-    <t>大鹅来了我家</t>
-  </si>
-  <si>
-    <t>雪对风鸟对虫</t>
-  </si>
-  <si>
     <t>月儿挂青天</t>
   </si>
   <si>
@@ -764,6 +755,15 @@
   </si>
   <si>
     <t>《家》</t>
+  </si>
+  <si>
+    <t>四是四，十是十</t>
+  </si>
+  <si>
+    <t>雪对风，鸟对虫</t>
+  </si>
+  <si>
+    <t>大鹅来我家了</t>
   </si>
 </sst>
 </file>
@@ -2569,7 +2569,7 @@
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
@@ -2668,7 +2668,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>32</v>
@@ -2682,31 +2682,31 @@
         <v>236</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{113C0928-7D5A-4257-984C-AAC657BCBC39}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FF79C10-1F4A-47FA-8D6C-D0B14F3FC7A8}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="245">
   <si>
     <t>an</t>
   </si>
@@ -757,13 +757,10 @@
     <t>《家》</t>
   </si>
   <si>
-    <t>四是四，十是十</t>
-  </si>
-  <si>
-    <t>雪对风，鸟对虫</t>
-  </si>
-  <si>
     <t>大鹅来我家了</t>
+  </si>
+  <si>
+    <t>鸟对虫</t>
   </si>
 </sst>
 </file>
@@ -2668,7 +2665,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>32</v>
@@ -2682,7 +2679,7 @@
         <v>236</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
@@ -2690,7 +2687,7 @@
         <v>237</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>244</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FF79C10-1F4A-47FA-8D6C-D0B14F3FC7A8}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F0CAFB3-C58A-433F-B357-838627A554A9}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="291">
   <si>
     <t>an</t>
   </si>
@@ -761,6 +761,144 @@
   </si>
   <si>
     <t>鸟对虫</t>
+  </si>
+  <si>
+    <t>《说话》</t>
+  </si>
+  <si>
+    <t>说话</t>
+  </si>
+  <si>
+    <t>说舌</t>
+  </si>
+  <si>
+    <t>兑话</t>
+  </si>
+  <si>
+    <t>土地</t>
+  </si>
+  <si>
+    <t>土他</t>
+  </si>
+  <si>
+    <t>土她</t>
+  </si>
+  <si>
+    <t>你好</t>
+  </si>
+  <si>
+    <t>尔好</t>
+  </si>
+  <si>
+    <t>你女</t>
+  </si>
+  <si>
+    <t>他们</t>
+  </si>
+  <si>
+    <t>他门</t>
+  </si>
+  <si>
+    <t>也们</t>
+  </si>
+  <si>
+    <t>儿子也去</t>
+  </si>
+  <si>
+    <t>几子也去</t>
+  </si>
+  <si>
+    <t>儿子也云</t>
+  </si>
+  <si>
+    <t>水杯</t>
+  </si>
+  <si>
+    <t>永杯</t>
+  </si>
+  <si>
+    <t>水不</t>
+  </si>
+  <si>
+    <t>小贝</t>
+  </si>
+  <si>
+    <t>小见</t>
+  </si>
+  <si>
+    <t>水贝</t>
+  </si>
+  <si>
+    <t>对比</t>
+  </si>
+  <si>
+    <t>树比</t>
+  </si>
+  <si>
+    <t>又比</t>
+  </si>
+  <si>
+    <t>我是天鹅</t>
+  </si>
+  <si>
+    <t>我是大鹅</t>
+  </si>
+  <si>
+    <t>我是太鹅</t>
+  </si>
+  <si>
+    <t>园子</t>
+  </si>
+  <si>
+    <t>园了</t>
+  </si>
+  <si>
+    <t>元子</t>
+  </si>
+  <si>
+    <t>大河</t>
+  </si>
+  <si>
+    <t>大可</t>
+  </si>
+  <si>
+    <t>天河</t>
+  </si>
+  <si>
+    <t>佳毛巾</t>
+  </si>
+  <si>
+    <t>清山</t>
+  </si>
+  <si>
+    <t>白天鹅说话</t>
+  </si>
+  <si>
+    <t>他们是对的</t>
+  </si>
+  <si>
+    <t>冲一冲手</t>
+  </si>
+  <si>
+    <t>妈妈的白马</t>
+  </si>
+  <si>
+    <t>雪片不见了</t>
+  </si>
+  <si>
+    <t>花儿好红</t>
+  </si>
+  <si>
+    <t>你出来</t>
+  </si>
+  <si>
+    <t>河边的树木</t>
+  </si>
+  <si>
+    <t>白天的雪地</t>
+  </si>
+  <si>
+    <t>园子也是他们家的</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.53125" customWidth="1"/>
@@ -2459,6 +2597,230 @@
         <v>201</v>
       </c>
     </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>245</v>
+      </c>
+      <c r="B89" t="s">
+        <v>245</v>
+      </c>
+      <c r="C89" t="s">
+        <v>245</v>
+      </c>
+      <c r="D89" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>246</v>
+      </c>
+      <c r="B90" t="s">
+        <v>247</v>
+      </c>
+      <c r="C90" t="s">
+        <v>248</v>
+      </c>
+      <c r="D90" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>249</v>
+      </c>
+      <c r="B91" t="s">
+        <v>249</v>
+      </c>
+      <c r="C91" t="s">
+        <v>250</v>
+      </c>
+      <c r="D91" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>252</v>
+      </c>
+      <c r="B92" t="s">
+        <v>253</v>
+      </c>
+      <c r="C92" t="s">
+        <v>252</v>
+      </c>
+      <c r="D92" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>255</v>
+      </c>
+      <c r="B93" t="s">
+        <v>256</v>
+      </c>
+      <c r="C93" t="s">
+        <v>255</v>
+      </c>
+      <c r="D93" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>258</v>
+      </c>
+      <c r="B94" t="s">
+        <v>259</v>
+      </c>
+      <c r="C94" t="s">
+        <v>258</v>
+      </c>
+      <c r="D94" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>211</v>
+      </c>
+      <c r="B95" t="s">
+        <v>211</v>
+      </c>
+      <c r="C95" t="s">
+        <v>212</v>
+      </c>
+      <c r="D95" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>261</v>
+      </c>
+      <c r="B96" t="s">
+        <v>262</v>
+      </c>
+      <c r="C96" t="s">
+        <v>263</v>
+      </c>
+      <c r="D96" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>264</v>
+      </c>
+      <c r="B97" t="s">
+        <v>265</v>
+      </c>
+      <c r="C97" t="s">
+        <v>264</v>
+      </c>
+      <c r="D97" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>267</v>
+      </c>
+      <c r="B98" t="s">
+        <v>268</v>
+      </c>
+      <c r="C98" t="s">
+        <v>267</v>
+      </c>
+      <c r="D98" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>270</v>
+      </c>
+      <c r="B99" t="s">
+        <v>271</v>
+      </c>
+      <c r="C99" t="s">
+        <v>272</v>
+      </c>
+      <c r="D99" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>273</v>
+      </c>
+      <c r="B100" t="s">
+        <v>274</v>
+      </c>
+      <c r="C100" t="s">
+        <v>273</v>
+      </c>
+      <c r="D100" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>276</v>
+      </c>
+      <c r="B101" t="s">
+        <v>276</v>
+      </c>
+      <c r="C101" t="s">
+        <v>277</v>
+      </c>
+      <c r="D101" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>170</v>
+      </c>
+      <c r="B102" t="s">
+        <v>172</v>
+      </c>
+      <c r="C102" t="s">
+        <v>170</v>
+      </c>
+      <c r="D102" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>232</v>
+      </c>
+      <c r="B103" t="s">
+        <v>279</v>
+      </c>
+      <c r="C103" t="s">
+        <v>232</v>
+      </c>
+      <c r="D103" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>164</v>
+      </c>
+      <c r="B104" t="s">
+        <v>164</v>
+      </c>
+      <c r="C104" t="s">
+        <v>280</v>
+      </c>
+      <c r="D104" t="s">
+        <v>166</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2466,11 +2828,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17.796875" style="4" customWidth="1"/>
     <col min="3" max="3" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -2706,6 +3068,49 @@
         <v>241</v>
       </c>
     </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D34" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F0CAFB3-C58A-433F-B357-838627A554A9}"/>
+  <xr:revisionPtr revIDLastSave="269" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70CFFAEC-0E38-444A-93F9-989EC2CD1F91}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="302">
   <si>
     <t>an</t>
   </si>
@@ -899,6 +899,39 @@
   </si>
   <si>
     <t>园子也是他们家的</t>
+  </si>
+  <si>
+    <t>《古朗月行》</t>
+  </si>
+  <si>
+    <t>月儿在天上</t>
+  </si>
+  <si>
+    <t>行李在台上</t>
+  </si>
+  <si>
+    <t>鸟儿又飞了</t>
+  </si>
+  <si>
+    <t>古人的家</t>
+  </si>
+  <si>
+    <t>玉又不是王</t>
+  </si>
+  <si>
+    <t>小时不说话</t>
+  </si>
+  <si>
+    <t>他们是好人</t>
+  </si>
+  <si>
+    <t>你十四了</t>
+  </si>
+  <si>
+    <t>挂出去</t>
+  </si>
+  <si>
+    <t>杯子在家</t>
   </si>
 </sst>
 </file>
@@ -2828,12 +2861,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.1328125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.796875" style="4" customWidth="1"/>
     <col min="3" max="3" width="9" style="4"/>
+    <col min="4" max="4" width="16.53125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
@@ -3111,6 +3145,49 @@
         <v>290</v>
       </c>
     </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D40" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/一上题库/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="269" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70CFFAEC-0E38-444A-93F9-989EC2CD1F91}"/>
+  <xr:revisionPtr revIDLastSave="288" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84AD6147-3848-4117-B372-851B3B44DDB3}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="317">
   <si>
     <t>an</t>
   </si>
@@ -932,6 +932,51 @@
   </si>
   <si>
     <t>杯子在家</t>
+  </si>
+  <si>
+    <t>《小小的船》</t>
+  </si>
+  <si>
+    <t>两头尖尖</t>
+  </si>
+  <si>
+    <t>坐在台上</t>
+  </si>
+  <si>
+    <t>闪闪的星星</t>
+  </si>
+  <si>
+    <t>只看红花</t>
+  </si>
+  <si>
+    <t>行李不见了</t>
+  </si>
+  <si>
+    <t>他们在说话</t>
+  </si>
+  <si>
+    <t>你比我大</t>
+  </si>
+  <si>
+    <t>妈妈好看</t>
+  </si>
+  <si>
+    <t>比一比水杯</t>
+  </si>
+  <si>
+    <t>冲冲小手</t>
+  </si>
+  <si>
+    <t>一片山林</t>
+  </si>
+  <si>
+    <t>说一说口令</t>
+  </si>
+  <si>
+    <t>小鸟飞出去</t>
+  </si>
+  <si>
+    <t>鱼儿在河里</t>
   </si>
 </sst>
 </file>
@@ -2861,12 +2906,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.1328125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.796875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9" style="4"/>
+    <col min="3" max="3" width="13.46484375" style="4" customWidth="1"/>
     <col min="4" max="4" width="16.53125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3188,6 +3233,64 @@
         <v>301</v>
       </c>
     </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D46" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/一上题库/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="288" documentId="13_ncr:1_{D4106D89-96B7-4863-817B-04B15C7F2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84AD6147-3848-4117-B372-851B3B44DDB3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="328">
   <si>
     <t>an</t>
   </si>
@@ -977,6 +977,39 @@
   </si>
   <si>
     <t>鱼儿在河里</t>
+  </si>
+  <si>
+    <t>大小多少</t>
+  </si>
+  <si>
+    <t>四个苹果</t>
+  </si>
+  <si>
+    <t>《大小多少》</t>
+  </si>
+  <si>
+    <t>三只黄牛</t>
+  </si>
+  <si>
+    <t>你多大了</t>
+  </si>
+  <si>
+    <t>去黄山</t>
+  </si>
+  <si>
+    <t>小黄牛</t>
+  </si>
+  <si>
+    <t>多几个苹果</t>
+  </si>
+  <si>
+    <t>挂果子</t>
+  </si>
+  <si>
+    <t>河边的花园</t>
+  </si>
+  <si>
+    <t>出青山</t>
   </si>
 </sst>
 </file>
@@ -1062,10 +1095,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2906,7 +2935,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.1328125" style="4" bestFit="1" customWidth="1"/>
@@ -3269,7 +3298,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="4" t="s">
         <v>305</v>
       </c>
@@ -3280,7 +3309,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="4" t="s">
         <v>307</v>
       </c>
@@ -3289,6 +3318,49 @@
       </c>
       <c r="C50" s="4" t="s">
         <v>316</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D52" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A54" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A55" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A56" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenji\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{423DDC01-6AA2-4146-BD0A-5291FC310510}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="339">
   <si>
     <t>an</t>
   </si>
@@ -1010,6 +1010,39 @@
   </si>
   <si>
     <t>出青山</t>
+  </si>
+  <si>
+    <t>《小书包》</t>
+  </si>
+  <si>
+    <t>你的书包大</t>
+  </si>
+  <si>
+    <t>地上的苹果</t>
+  </si>
+  <si>
+    <t>本地人</t>
+  </si>
+  <si>
+    <t>你真好</t>
+  </si>
+  <si>
+    <t>一边多一边少</t>
+  </si>
+  <si>
+    <t>一个大一个小</t>
+  </si>
+  <si>
+    <t>一头黄牛</t>
+  </si>
+  <si>
+    <t>我们也说了好多话</t>
+  </si>
+  <si>
+    <t>他的刀子</t>
+  </si>
+  <si>
+    <t>你的笔</t>
   </si>
 </sst>
 </file>
@@ -1361,16 +1394,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F104"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="12.53125" customWidth="1"/>
+    <col min="1" max="1" width="12.5234375" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="16.86328125" customWidth="1"/>
-    <col min="4" max="4" width="21.1328125" customWidth="1"/>
-    <col min="5" max="5" width="18.1328125" customWidth="1"/>
+    <col min="3" max="3" width="16.83984375" customWidth="1"/>
+    <col min="4" max="4" width="21.1015625" customWidth="1"/>
+    <col min="5" max="5" width="18.1015625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1390,7 +1423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1410,7 +1443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1430,7 +1463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1450,7 +1483,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -1470,7 +1503,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1490,7 +1523,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -1510,7 +1543,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1530,7 +1563,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -1550,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -1570,7 +1603,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -1590,7 +1623,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1610,7 +1643,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -1630,7 +1663,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -1650,7 +1683,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>69</v>
       </c>
@@ -1670,7 +1703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -1690,7 +1723,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>208</v>
       </c>
@@ -1704,7 +1737,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>208</v>
       </c>
@@ -1721,7 +1754,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -1735,7 +1768,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>77</v>
       </c>
@@ -1749,7 +1782,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>80</v>
       </c>
@@ -1763,7 +1796,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>85</v>
       </c>
@@ -1777,7 +1810,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>86</v>
       </c>
@@ -1791,7 +1824,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>89</v>
       </c>
@@ -1805,7 +1838,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>92</v>
       </c>
@@ -1819,7 +1852,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -1833,7 +1866,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -1847,7 +1880,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>97</v>
       </c>
@@ -1861,7 +1894,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -1875,7 +1908,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>102</v>
       </c>
@@ -1889,7 +1922,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>104</v>
       </c>
@@ -1903,7 +1936,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>107</v>
       </c>
@@ -1917,7 +1950,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -1931,7 +1964,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>209</v>
       </c>
@@ -1945,7 +1978,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>209</v>
       </c>
@@ -1959,7 +1992,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>113</v>
       </c>
@@ -1973,7 +2006,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>116</v>
       </c>
@@ -1987,7 +2020,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>119</v>
       </c>
@@ -2001,7 +2034,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -2015,7 +2048,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>125</v>
       </c>
@@ -2029,7 +2062,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>128</v>
       </c>
@@ -2043,7 +2076,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>107</v>
       </c>
@@ -2057,7 +2090,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>86</v>
       </c>
@@ -2071,7 +2104,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -2085,7 +2118,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>83</v>
       </c>
@@ -2099,7 +2132,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>136</v>
       </c>
@@ -2113,7 +2146,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>80</v>
       </c>
@@ -2127,7 +2160,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>97</v>
       </c>
@@ -2141,7 +2174,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -2155,7 +2188,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2169,7 +2202,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>85</v>
       </c>
@@ -2183,7 +2216,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>145</v>
       </c>
@@ -2197,7 +2230,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>163</v>
       </c>
@@ -2211,7 +2244,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>163</v>
       </c>
@@ -2228,7 +2261,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>160</v>
       </c>
@@ -2242,7 +2275,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>164</v>
       </c>
@@ -2256,7 +2289,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>167</v>
       </c>
@@ -2270,7 +2303,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>170</v>
       </c>
@@ -2284,7 +2317,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>173</v>
       </c>
@@ -2298,7 +2331,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>176</v>
       </c>
@@ -2312,7 +2345,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>179</v>
       </c>
@@ -2326,7 +2359,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>182</v>
       </c>
@@ -2340,7 +2373,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>185</v>
       </c>
@@ -2354,7 +2387,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>113</v>
       </c>
@@ -2368,7 +2401,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>119</v>
       </c>
@@ -2382,7 +2415,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>190</v>
       </c>
@@ -2396,7 +2429,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>193</v>
       </c>
@@ -2410,7 +2443,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>196</v>
       </c>
@@ -2424,7 +2457,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>199</v>
       </c>
@@ -2438,7 +2471,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>80</v>
       </c>
@@ -2452,7 +2485,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>202</v>
       </c>
@@ -2466,7 +2499,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>205</v>
       </c>
@@ -2480,7 +2513,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>210</v>
       </c>
@@ -2494,7 +2527,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>211</v>
       </c>
@@ -2508,7 +2541,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>214</v>
       </c>
@@ -2522,7 +2555,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>217</v>
       </c>
@@ -2536,7 +2569,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>190</v>
       </c>
@@ -2550,7 +2583,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>221</v>
       </c>
@@ -2564,7 +2597,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>224</v>
       </c>
@@ -2578,7 +2611,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>227</v>
       </c>
@@ -2592,7 +2625,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>160</v>
       </c>
@@ -2606,7 +2639,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>164</v>
       </c>
@@ -2620,7 +2653,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>232</v>
       </c>
@@ -2634,7 +2667,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>170</v>
       </c>
@@ -2648,7 +2681,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>173</v>
       </c>
@@ -2662,7 +2695,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>182</v>
       </c>
@@ -2676,7 +2709,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>74</v>
       </c>
@@ -2690,7 +2723,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>199</v>
       </c>
@@ -2704,7 +2737,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>245</v>
       </c>
@@ -2718,7 +2751,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>246</v>
       </c>
@@ -2732,7 +2765,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>249</v>
       </c>
@@ -2746,7 +2779,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>252</v>
       </c>
@@ -2760,7 +2793,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>255</v>
       </c>
@@ -2774,7 +2807,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>258</v>
       </c>
@@ -2788,7 +2821,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>211</v>
       </c>
@@ -2802,7 +2835,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>261</v>
       </c>
@@ -2816,7 +2849,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>264</v>
       </c>
@@ -2830,7 +2863,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>267</v>
       </c>
@@ -2844,7 +2877,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>270</v>
       </c>
@@ -2858,7 +2891,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>273</v>
       </c>
@@ -2872,7 +2905,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>276</v>
       </c>
@@ -2886,7 +2919,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>170</v>
       </c>
@@ -2900,7 +2933,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>232</v>
       </c>
@@ -2914,7 +2947,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>164</v>
       </c>
@@ -2935,16 +2968,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:D62"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="16.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.796875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.46484375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.53125" customWidth="1"/>
+    <col min="1" max="1" width="16.1015625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7890625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.47265625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.5234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -2955,7 +2988,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -2966,7 +2999,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -2977,7 +3010,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -2988,7 +3021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -2999,7 +3032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
@@ -3008,27 +3041,27 @@
       </c>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3039,7 +3072,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3047,7 +3080,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3055,7 +3088,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3063,7 +3096,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3071,7 +3104,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3079,13 +3112,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>32</v>
       </c>
       <c r="B17"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4" t="s">
         <v>152</v>
       </c>
@@ -3093,7 +3126,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="4" t="s">
         <v>153</v>
       </c>
@@ -3101,7 +3134,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="4" t="s">
         <v>154</v>
       </c>
@@ -3109,7 +3142,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4" t="s">
         <v>151</v>
       </c>
@@ -3117,7 +3150,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4" t="s">
         <v>148</v>
       </c>
@@ -3125,7 +3158,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4" t="s">
         <v>157</v>
       </c>
@@ -3133,7 +3166,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4" t="s">
         <v>244</v>
       </c>
@@ -3144,7 +3177,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4" t="s">
         <v>236</v>
       </c>
@@ -3152,7 +3185,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4" t="s">
         <v>237</v>
       </c>
@@ -3160,7 +3193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4" t="s">
         <v>238</v>
       </c>
@@ -3168,7 +3201,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4" t="s">
         <v>239</v>
       </c>
@@ -3176,7 +3209,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4" t="s">
         <v>281</v>
       </c>
@@ -3187,7 +3220,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="4" t="s">
         <v>282</v>
       </c>
@@ -3195,7 +3228,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="4" t="s">
         <v>283</v>
       </c>
@@ -3203,7 +3236,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4" t="s">
         <v>284</v>
       </c>
@@ -3211,7 +3244,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="4" t="s">
         <v>285</v>
       </c>
@@ -3219,7 +3252,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="4" t="s">
         <v>292</v>
       </c>
@@ -3230,7 +3263,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="4" t="s">
         <v>293</v>
       </c>
@@ -3238,7 +3271,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="4" t="s">
         <v>294</v>
       </c>
@@ -3246,7 +3279,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="4" t="s">
         <v>295</v>
       </c>
@@ -3254,7 +3287,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="4" t="s">
         <v>296</v>
       </c>
@@ -3262,7 +3295,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="4" t="s">
         <v>303</v>
       </c>
@@ -3276,7 +3309,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="4" t="s">
         <v>304</v>
       </c>
@@ -3287,7 +3320,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="4" t="s">
         <v>306</v>
       </c>
@@ -3298,7 +3331,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="4" t="s">
         <v>305</v>
       </c>
@@ -3309,7 +3342,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="4" t="s">
         <v>307</v>
       </c>
@@ -3320,7 +3353,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="4" t="s">
         <v>317</v>
       </c>
@@ -3331,7 +3364,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="4" t="s">
         <v>320</v>
       </c>
@@ -3339,7 +3372,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="4" t="s">
         <v>322</v>
       </c>
@@ -3347,7 +3380,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="4" t="s">
         <v>324</v>
       </c>
@@ -3355,12 +3388,55 @@
         <v>325</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="4" t="s">
         <v>326</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>327</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D58" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{423DDC01-6AA2-4146-BD0A-5291FC310510}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{327A2631-75D8-464A-A229-A182B6F7C9EB}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1036,13 +1036,13 @@
     <t>一头黄牛</t>
   </si>
   <si>
-    <t>我们也说了好多话</t>
-  </si>
-  <si>
     <t>他的刀子</t>
   </si>
   <si>
-    <t>你的笔</t>
+    <t>说了好多话</t>
+  </si>
+  <si>
+    <t>我们的笔</t>
   </si>
 </sst>
 </file>
@@ -1128,6 +1128,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3412,7 +3416,7 @@
         <v>330</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -3433,7 +3437,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>334</v>
